--- a/_data/PLCTags_ControlPanel.xlsx
+++ b/_data/PLCTags_ControlPanel.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC Tags" sheetId="1" r:id="R8aa00fc0d2df41ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="R7f68a9c902814e00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC Tags" sheetId="1" r:id="R61549055a1ae475a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="Reaa3eb21638645d9"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="64">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="70">
   <x:si>
     <x:t xml:space="preserve">Name</x:t>
   </x:si>
@@ -137,64 +137,82 @@
     <x:t xml:space="preserve">SignalTower_Yellow</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">%Q1.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ampel "Lampe Einrichten aktiv" (gelb)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BT1_ControlOnOff</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%I0.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1 = Steuerung Ein (einrastend)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SignalTower_Green</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">%Q1.1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Ampel "Lampe Einrichten aktiv" (gelb)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BT1_ControlOnOff</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">%I0.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 = Steuerung Ein (einrastend)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SignalTower_Green</x:t>
+    <x:t xml:space="preserve">Ampel "Automatik läuft" (grün)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SignalTower_Red</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q1.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ampel "Störung" (rot)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BT3_SingleStepLight</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q0.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tasterbeleuchtung "Einzelschritt läuft" (grün)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BT7_HomingLight</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q0.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tasterbeleuchtung "Grundstellungsfahrt läuft" (green)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BT5_AutoStopLight</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q0.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tasterbeleuchtung "Automatik Stop läuft" (blau)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BT8_ImmediateStop</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%I1.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Sofort Halt</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BT8_ImmediateStopLight</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">%Q1.0</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Ampel "Automatik läuft" (grün)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SignalTower_Red</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">%Q1.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Ampel "Störung" (rot)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BT3_SingleStepLight</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">%Q0.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tasterbeleuchtung "Einzelschritt läuft" (grün)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BT7_HomingLight</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">%Q0.7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tasterbeleuchtung "Grundstellungsfahrt läuft" (green)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BT5_AutoStopLight</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">%Q0.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tasterbeleuchtung "Automatik Stop läuft" (blau)</x:t>
+    <x:t xml:space="preserve">Tasterbeleuchtung "Sofort Halt" (rot)</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">BelongsToUnit</x:t>
@@ -798,6 +816,70 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
@@ -810,10 +892,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
